--- a/artfynd/A 39705-2023 artfynd.xlsx
+++ b/artfynd/A 39705-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39705-2023 artfynd.xlsx
+++ b/artfynd/A 39705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1468,127 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123777940</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkyrkberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>397876</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6646156</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39705-2023 artfynd.xlsx
+++ b/artfynd/A 39705-2023 artfynd.xlsx
@@ -1473,7 +1473,7 @@
         <v>123777940</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 39705-2023 artfynd.xlsx
+++ b/artfynd/A 39705-2023 artfynd.xlsx
@@ -1473,7 +1473,7 @@
         <v>123777940</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 39705-2023 artfynd.xlsx
+++ b/artfynd/A 39705-2023 artfynd.xlsx
@@ -1473,7 +1473,7 @@
         <v>123777940</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
